--- a/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlFundAcctPosi001.xlsx
+++ b/tams-invest-parent/tams-invest-portfolio/src/main/resources/tpl/PtlFundAcctPosi001.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20378"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{032499B7-2AB0-440F-B4BB-E9A6C9FFE614}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="12915" windowHeight="5985"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="12915" windowHeight="5985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>组合代码</t>
   </si>
@@ -39,13 +39,17 @@
   </si>
   <si>
     <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>账户类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -102,7 +106,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -177,6 +181,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -212,6 +233,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -387,8 +425,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
@@ -396,12 +434,12 @@
     <col min="3" max="3" width="19.75" customWidth="1"/>
     <col min="4" max="4" width="20.25" customWidth="1"/>
     <col min="5" max="5" width="18.75" customWidth="1"/>
-    <col min="6" max="6" width="18.25" customWidth="1"/>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
-    <col min="8" max="9" width="15.625" customWidth="1"/>
+    <col min="6" max="7" width="18.25" customWidth="1"/>
+    <col min="8" max="8" width="16.875" customWidth="1"/>
+    <col min="9" max="10" width="15.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -418,12 +456,15 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
     </row>
